--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9254252831</v>
+        <v>46157.93118286148</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118286148</v>
+        <v>46157.93370093868</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93370093868</v>
+        <v>46157.93674754832</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93674754832</v>
+        <v>46158.28196052072</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28196052072</v>
+        <v>46158.29720702307</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29720702307</v>
+        <v>46158.29792798801</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29792798801</v>
+        <v>46158.33357534303</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33357534303</v>
+        <v>46158.37211765082</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37211765082</v>
+        <v>46158.37268678773</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
